--- a/Phase - 10 API Testing/lms/src/test/resources/testData/InvalidLoginData.xlsx
+++ b/Phase - 10 API Testing/lms/src/test/resources/testData/InvalidLoginData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EXPLEO SMARTCLIFF\Phase - 10 API Testing\lms\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65CE332-4F45-4FA7-86F4-89F0033A3B3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF85382-CA7A-4CFE-BB2D-83766B5814F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
